--- a/public/modelo-produtos.xlsx
+++ b/public/modelo-produtos.xlsx
@@ -22,40 +22,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF0F2733"/>
+        <fgColor rgb="FF0E7A5F"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
-    <border/>
+  <borders count="1">
     <border>
-      <left style="thin">
-        <color rgb="FFD9E2EA"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFD9E2EA"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFD9E2EA"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFD9E2EA"/>
-      </bottom>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="1" defaultTableStyle="TableStyleMedium4" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl\tables\table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="TabelaProdutos" displayName="TabelaProdutos" ref="A1:K4" totalsRowShown="0">
+  <autoFilter ref="A1:K4"/>
+  <tableColumns count="11">
+    <tableColumn id="1" name="nome"/>
+    <tableColumn id="2" name="descricao"/>
+    <tableColumn id="3" name="preco"/>
+    <tableColumn id="4" name="categoria"/>
+    <tableColumn id="5" name="subcategoria"/>
+    <tableColumn id="6" name="imagem_1"/>
+    <tableColumn id="7" name="imagem_2"/>
+    <tableColumn id="8" name="imagem_3"/>
+    <tableColumn id="9" name="imagem_4"/>
+    <tableColumn id="10" name="novidade"/>
+    <tableColumn id="11" name="ativo"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium4" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl\workbook.xml><?xml version="1.0" encoding="utf-8"?>
@@ -67,13 +81,14 @@
 </file>
 
 <file path=xl\worksheets\sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:K4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="24" customWidth="1"/>
-    <col min="2" max="2" width="38" customWidth="1"/>
+    <col min="1" max="1" width="28" customWidth="1"/>
+    <col min="2" max="2" width="42" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="5" width="28" customWidth="1"/>
+    <col min="4" max="5" width="30" customWidth="1"/>
     <col min="6" max="9" width="36" customWidth="1"/>
     <col min="10" max="11" width="12" customWidth="1"/>
   </cols>
@@ -154,9 +169,29 @@
           <t>Acessorios Para Bicicletas e Motos</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F2" t="inlineStr" s="0">
         <is>
-          <t>https://exemplo.com/imagem1.jpg</t>
+          <t>https://exemplo.com/produto-1.jpg</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr" s="0">
+        <is>
+          <t/>
         </is>
       </c>
       <c r="J2" t="inlineStr" s="0">
@@ -189,9 +224,29 @@
           <t>Adaptador de Tomadas</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F3" t="inlineStr" s="0">
         <is>
-          <t>https://exemplo.com/adaptador.jpg</t>
+          <t>https://exemplo.com/produto-2.jpg</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr" s="0">
+        <is>
+          <t/>
         </is>
       </c>
       <c r="J3" t="inlineStr" s="0">
@@ -224,9 +279,29 @@
           <t>Produtos Infantis</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
       <c r="F4" t="inlineStr" s="0">
         <is>
-          <t>https://exemplo.com/produto.jpg</t>
+          <t>https://exemplo.com/produto-3.jpg</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr" s="0">
+        <is>
+          <t>https://exemplo.com/produto-3b.jpg</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr" s="0">
+        <is>
+          <t/>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr" s="0">
+        <is>
+          <t/>
         </is>
       </c>
       <c r="J4" t="inlineStr" s="0">
@@ -241,14 +316,16 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K1"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" sqref="J2:J500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J200">
       <formula1>"sim,nao"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K500">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K200">
       <formula1>"sim,nao"</formula1>
     </dataValidation>
   </dataValidations>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
--- a/public/modelo-produtos.xlsx
+++ b/public/modelo-produtos.xlsx
@@ -76,6 +76,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <sheets>
     <sheet name="Produtos" sheetId="1" r:id="rId1"/>
+    <sheet name="Novidades" sheetId="2" r:id="rId2"/>
   </sheets>
 </workbook>
 </file>
@@ -90,7 +91,7 @@
     <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="5" width="30" customWidth="1"/>
     <col min="6" max="9" width="36" customWidth="1"/>
-    <col min="10" max="11" width="12" customWidth="1"/>
+    <col min="10" max="11" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -196,12 +197,12 @@
       </c>
       <c r="J2" t="inlineStr" s="0">
         <is>
-          <t>sim</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K2" t="inlineStr" s="0">
         <is>
-          <t>sim</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -251,12 +252,12 @@
       </c>
       <c r="J3" t="inlineStr" s="0">
         <is>
-          <t>nao</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="K3" t="inlineStr" s="0">
         <is>
-          <t>sim</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
@@ -306,26 +307,59 @@
       </c>
       <c r="J4" t="inlineStr" s="0">
         <is>
-          <t>sim</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="K4" t="inlineStr" s="0">
         <is>
-          <t>sim</t>
+          <t>Sim</t>
         </is>
       </c>
     </row>
   </sheetData>
   <dataValidations count="2">
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="J2:J200">
-      <formula1>"sim,nao"</formula1>
+      <formula1>"Sim,Não"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" sqref="K2:K200">
-      <formula1>"sim,nao"</formula1>
+      <formula1>"Sim,Não"</formula1>
     </dataValidation>
   </dataValidations>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl\worksheets\sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:A3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr" s="1">
+        <is>
+          <t>Opcoes para Novidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Sim</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Não</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+</worksheet>
 </file>